--- a/cohr/dist/20261025_Coherent模型_v0.2.1.xlsx
+++ b/cohr/dist/20261025_Coherent模型_v0.2.1.xlsx
@@ -5770,7 +5770,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5988,7 +5988,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6109,7 +6109,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6230,7 +6230,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6351,7 +6351,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6472,7 +6472,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
